--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/132.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/132.xlsx
@@ -426,13 +426,13 @@
         <v>-28.12706703229808</v>
       </c>
       <c r="E2">
-        <v>-7.26201243505004</v>
+        <v>-10.19217059866116</v>
       </c>
       <c r="F2">
-        <v>0.1088704262745977</v>
+        <v>-0.9661958684502047</v>
       </c>
       <c r="G2">
-        <v>-11.6738752588886</v>
+        <v>-12.47784786419169</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-27.04008417151958</v>
       </c>
       <c r="E3">
-        <v>-9.081281582891529</v>
+        <v>-9.344911225722067</v>
       </c>
       <c r="F3">
-        <v>0.3062001833383529</v>
+        <v>-0.7893909400505448</v>
       </c>
       <c r="G3">
-        <v>-10.91277752886462</v>
+        <v>-11.58638747192228</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-25.66101537041238</v>
       </c>
       <c r="E4">
-        <v>-9.392663984132952</v>
+        <v>-10.28893050278305</v>
       </c>
       <c r="F4">
-        <v>0.3001456756236279</v>
+        <v>-1.060063701764216</v>
       </c>
       <c r="G4">
-        <v>-10.61042209421744</v>
+        <v>-10.47915896358534</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-24.17338605954651</v>
       </c>
       <c r="E5">
-        <v>-9.950341029703548</v>
+        <v>-10.2848231768581</v>
       </c>
       <c r="F5">
-        <v>0.009444577050351493</v>
+        <v>-0.5766097562228046</v>
       </c>
       <c r="G5">
-        <v>-10.44337196630582</v>
+        <v>-10.51944830279827</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-22.6424561612445</v>
       </c>
       <c r="E6">
-        <v>-10.46506549931139</v>
+        <v>-13.57296626772357</v>
       </c>
       <c r="F6">
-        <v>0.3803556291228896</v>
+        <v>-0.8863034479869886</v>
       </c>
       <c r="G6">
-        <v>-10.2649170090114</v>
+        <v>-10.07571602089652</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.16079612455226</v>
       </c>
       <c r="E7">
-        <v>-11.54492541118046</v>
+        <v>-12.75388306006021</v>
       </c>
       <c r="F7">
-        <v>0.3798512187888221</v>
+        <v>-0.5286115891906236</v>
       </c>
       <c r="G7">
-        <v>-9.033847613141402</v>
+        <v>-10.85447220082697</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.8038712596993</v>
       </c>
       <c r="E8">
-        <v>-12.20368252507627</v>
+        <v>-13.91227123969629</v>
       </c>
       <c r="F8">
-        <v>0.2780616884857825</v>
+        <v>-1.032476336570219</v>
       </c>
       <c r="G8">
-        <v>-8.723728949204634</v>
+        <v>-9.257580901776429</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.64205628296783</v>
       </c>
       <c r="E9">
-        <v>-12.99626510284675</v>
+        <v>-13.71846613759002</v>
       </c>
       <c r="F9">
-        <v>0.3084878465332052</v>
+        <v>-0.4381431806241028</v>
       </c>
       <c r="G9">
-        <v>-7.878967112312188</v>
+        <v>-8.711344198342221</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.68408892374643</v>
       </c>
       <c r="E10">
-        <v>-12.73544311390097</v>
+        <v>-15.39823111515122</v>
       </c>
       <c r="F10">
-        <v>0.489172062572734</v>
+        <v>-0.1826153985797789</v>
       </c>
       <c r="G10">
-        <v>-7.003526449907316</v>
+        <v>-7.489123890698692</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.94496031507165</v>
       </c>
       <c r="E11">
-        <v>-13.69599584956396</v>
+        <v>-15.51227620456039</v>
       </c>
       <c r="F11">
-        <v>0.6620177261837953</v>
+        <v>-0.4875437192444055</v>
       </c>
       <c r="G11">
-        <v>-6.295837751068392</v>
+        <v>-7.738103399616199</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.39940494143906</v>
       </c>
       <c r="E12">
-        <v>-14.42775196446341</v>
+        <v>-17.00857005770082</v>
       </c>
       <c r="F12">
-        <v>0.5791756534530732</v>
+        <v>-0.2229523882460216</v>
       </c>
       <c r="G12">
-        <v>-6.311377451829731</v>
+        <v>-7.718865819487494</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.99157601152249</v>
       </c>
       <c r="E13">
-        <v>-15.39434568445264</v>
+        <v>-16.41778081018614</v>
       </c>
       <c r="F13">
-        <v>0.9412884273123875</v>
+        <v>0.04441280366325449</v>
       </c>
       <c r="G13">
-        <v>-4.969835151314251</v>
+        <v>-6.023247431364803</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.69274206258581</v>
       </c>
       <c r="E14">
-        <v>-16.59279727363458</v>
+        <v>-17.09919387954232</v>
       </c>
       <c r="F14">
-        <v>1.146129701533072</v>
+        <v>0.403301152278734</v>
       </c>
       <c r="G14">
-        <v>-4.796895562888263</v>
+        <v>-6.310139307798044</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.4578767153055</v>
       </c>
       <c r="E15">
-        <v>-16.66050701699727</v>
+        <v>-19.02151298190235</v>
       </c>
       <c r="F15">
-        <v>1.037625258148569</v>
+        <v>0.4617232716463375</v>
       </c>
       <c r="G15">
-        <v>-3.627342724228999</v>
+        <v>-5.92886708858572</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.25062690683597</v>
       </c>
       <c r="E16">
-        <v>-18.12401924679617</v>
+        <v>-20.78961490193118</v>
       </c>
       <c r="F16">
-        <v>1.696907777392772</v>
+        <v>0.7690809971852482</v>
       </c>
       <c r="G16">
-        <v>-3.332863077419748</v>
+        <v>-4.131651368408336</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.06573641860303</v>
       </c>
       <c r="E17">
-        <v>-19.22240514583063</v>
+        <v>-20.49695321223746</v>
       </c>
       <c r="F17">
-        <v>1.651802249215141</v>
+        <v>0.7505785609751692</v>
       </c>
       <c r="G17">
-        <v>-3.493212661159887</v>
+        <v>-4.748018668546463</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.88601897379189</v>
       </c>
       <c r="E18">
-        <v>-20.21214389647306</v>
+        <v>-22.00821820044726</v>
       </c>
       <c r="F18">
-        <v>1.962385983703802</v>
+        <v>1.419285714122152</v>
       </c>
       <c r="G18">
-        <v>-2.541649314625013</v>
+        <v>-4.637466310808041</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.70877787901672</v>
       </c>
       <c r="E19">
-        <v>-21.45891430331684</v>
+        <v>-22.47519896859223</v>
       </c>
       <c r="F19">
-        <v>1.969967183921011</v>
+        <v>1.65700472314736</v>
       </c>
       <c r="G19">
-        <v>-1.98181620066102</v>
+        <v>-4.250430431811846</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.5393861744825</v>
       </c>
       <c r="E20">
-        <v>-21.76457724188657</v>
+        <v>-23.48195572455548</v>
       </c>
       <c r="F20">
-        <v>2.482710978515517</v>
+        <v>1.719071741679347</v>
       </c>
       <c r="G20">
-        <v>-2.237194994105938</v>
+        <v>-3.596187180158918</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.36451104153619</v>
       </c>
       <c r="E21">
-        <v>-22.67625868605879</v>
+        <v>-24.5123103585727</v>
       </c>
       <c r="F21">
-        <v>2.674105005808205</v>
+        <v>1.815384816926797</v>
       </c>
       <c r="G21">
-        <v>-2.219321358739413</v>
+        <v>-3.007807232009789</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.1876629434957</v>
       </c>
       <c r="E22">
-        <v>-22.82505528500282</v>
+        <v>-25.47727382791916</v>
       </c>
       <c r="F22">
-        <v>2.577220212725281</v>
+        <v>2.031381715615837</v>
       </c>
       <c r="G22">
-        <v>-1.911596219227538</v>
+        <v>-2.864142797787576</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.01090151662341</v>
       </c>
       <c r="E23">
-        <v>-23.66981494028968</v>
+        <v>-26.02924046776609</v>
       </c>
       <c r="F23">
-        <v>2.701678909501922</v>
+        <v>1.715669941372983</v>
       </c>
       <c r="G23">
-        <v>-2.032258983042895</v>
+        <v>-3.606605466971004</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.8268865329318</v>
       </c>
       <c r="E24">
-        <v>-24.04358612793477</v>
+        <v>-25.96385836004334</v>
       </c>
       <c r="F24">
-        <v>2.661017260123014</v>
+        <v>2.2564896744364</v>
       </c>
       <c r="G24">
-        <v>-1.658975110216833</v>
+        <v>-2.805820917022236</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.65135520962473</v>
       </c>
       <c r="E25">
-        <v>-24.6960350775379</v>
+        <v>-25.77682785505255</v>
       </c>
       <c r="F25">
-        <v>2.543395421783326</v>
+        <v>1.330557006503742</v>
       </c>
       <c r="G25">
-        <v>-1.799494526176737</v>
+        <v>-3.167001435356722</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.4936337360509</v>
       </c>
       <c r="E26">
-        <v>-23.5058207825759</v>
+        <v>-26.3944030263226</v>
       </c>
       <c r="F26">
-        <v>2.31485398853809</v>
+        <v>1.6543931920928</v>
       </c>
       <c r="G26">
-        <v>-0.7907713003608068</v>
+        <v>-2.923825312769557</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.35620554625198</v>
       </c>
       <c r="E27">
-        <v>-25.05301015508854</v>
+        <v>-24.99378224354222</v>
       </c>
       <c r="F27">
-        <v>2.338429034795322</v>
+        <v>1.641842322712942</v>
       </c>
       <c r="G27">
-        <v>-1.564985411811384</v>
+        <v>-2.742993383777947</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-13.25957731624102</v>
       </c>
       <c r="E28">
-        <v>-24.00538844968008</v>
+        <v>-26.55468836382409</v>
       </c>
       <c r="F28">
-        <v>2.341029479908473</v>
+        <v>1.618682207405556</v>
       </c>
       <c r="G28">
-        <v>-1.807367003469124</v>
+        <v>-2.894871281483091</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-13.20509495376488</v>
       </c>
       <c r="E29">
-        <v>-24.32445567131251</v>
+        <v>-26.54027423105768</v>
       </c>
       <c r="F29">
-        <v>2.088979516054454</v>
+        <v>1.556730799405396</v>
       </c>
       <c r="G29">
-        <v>-1.906666816919564</v>
+        <v>-2.284750980777569</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-13.1894336155725</v>
       </c>
       <c r="E30">
-        <v>-23.91324758904601</v>
+        <v>-25.36936934926439</v>
       </c>
       <c r="F30">
-        <v>2.009830645518537</v>
+        <v>1.969431891321592</v>
       </c>
       <c r="G30">
-        <v>-1.948455833261784</v>
+        <v>-2.598511244807535</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.21837741582356</v>
       </c>
       <c r="E31">
-        <v>-23.39325650416724</v>
+        <v>-24.58228886741323</v>
       </c>
       <c r="F31">
-        <v>2.014805065798932</v>
+        <v>1.626605488100499</v>
       </c>
       <c r="G31">
-        <v>-1.711718721748501</v>
+        <v>-3.288654052288321</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-13.27922862826718</v>
       </c>
       <c r="E32">
-        <v>-23.04810074377662</v>
+        <v>-25.30316758774626</v>
       </c>
       <c r="F32">
-        <v>1.663713301405161</v>
+        <v>1.290810739143958</v>
       </c>
       <c r="G32">
-        <v>-1.957218847304235</v>
+        <v>-2.262199544564053</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-13.36524499805763</v>
       </c>
       <c r="E33">
-        <v>-22.29225314715636</v>
+        <v>-24.54460743519541</v>
       </c>
       <c r="F33">
-        <v>1.873342118608219</v>
+        <v>1.354379110883782</v>
       </c>
       <c r="G33">
-        <v>-2.062924566373164</v>
+        <v>-3.119415653775238</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.47358136752067</v>
       </c>
       <c r="E34">
-        <v>-22.85847089470542</v>
+        <v>-23.95881309451119</v>
       </c>
       <c r="F34">
-        <v>2.145639762591131</v>
+        <v>1.480071514568549</v>
       </c>
       <c r="G34">
-        <v>-2.19348917189648</v>
+        <v>-1.984017713444635</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.58613129294888</v>
       </c>
       <c r="E35">
-        <v>-21.1999444602402</v>
+        <v>-23.53022020052923</v>
       </c>
       <c r="F35">
-        <v>2.05083437537518</v>
+        <v>1.289843094829624</v>
       </c>
       <c r="G35">
-        <v>-1.785576992729641</v>
+        <v>-3.622496085559506</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.7021717259283</v>
       </c>
       <c r="E36">
-        <v>-21.27721381223308</v>
+        <v>-23.64765711697015</v>
       </c>
       <c r="F36">
-        <v>2.401897633062473</v>
+        <v>0.9896437200285001</v>
       </c>
       <c r="G36">
-        <v>-2.475593999479935</v>
+        <v>-1.743231804736824</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.81941989774935</v>
       </c>
       <c r="E37">
-        <v>-19.99854030600525</v>
+        <v>-23.70227957045067</v>
       </c>
       <c r="F37">
-        <v>2.060152900981625</v>
+        <v>1.070167247299019</v>
       </c>
       <c r="G37">
-        <v>-2.011402546145486</v>
+        <v>-3.027485114695217</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.92503244971624</v>
       </c>
       <c r="E38">
-        <v>-19.52444983366823</v>
+        <v>-22.11974092983415</v>
       </c>
       <c r="F38">
-        <v>2.4444486435985</v>
+        <v>1.524966409859427</v>
       </c>
       <c r="G38">
-        <v>-2.875928339907382</v>
+        <v>-2.899221338321694</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.02496475846312</v>
       </c>
       <c r="E39">
-        <v>-20.12845769681131</v>
+        <v>-21.0074843149142</v>
       </c>
       <c r="F39">
-        <v>2.543810352733171</v>
+        <v>1.736536850514813</v>
       </c>
       <c r="G39">
-        <v>-2.576221341691622</v>
+        <v>-2.942966887077623</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.11758909448565</v>
       </c>
       <c r="E40">
-        <v>-19.12852082270361</v>
+        <v>-21.40951770884117</v>
       </c>
       <c r="F40">
-        <v>2.349033529605104</v>
+        <v>1.509965547428384</v>
       </c>
       <c r="G40">
-        <v>-2.722272679247649</v>
+        <v>-3.193664569130013</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.19617520504535</v>
       </c>
       <c r="E41">
-        <v>-19.00780981955515</v>
+        <v>-21.0133260463841</v>
       </c>
       <c r="F41">
-        <v>2.453611966025233</v>
+        <v>1.417508796085029</v>
       </c>
       <c r="G41">
-        <v>-2.386272170284859</v>
+        <v>-2.34197707096941</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.272454778572</v>
       </c>
       <c r="E42">
-        <v>-18.08499285779807</v>
+        <v>-19.69279585490338</v>
       </c>
       <c r="F42">
-        <v>2.717865967663628</v>
+        <v>1.542830612585584</v>
       </c>
       <c r="G42">
-        <v>-2.639737468408079</v>
+        <v>-2.735163943577571</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.34395636596934</v>
       </c>
       <c r="E43">
-        <v>-17.05448425566459</v>
+        <v>-17.70696490458577</v>
       </c>
       <c r="F43">
-        <v>2.563348532611947</v>
+        <v>1.29499805758438</v>
       </c>
       <c r="G43">
-        <v>-3.805228267690657</v>
+        <v>-2.790125620620551</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.4082607168765</v>
       </c>
       <c r="E44">
-        <v>-15.86003130903142</v>
+        <v>-18.95503045499575</v>
       </c>
       <c r="F44">
-        <v>2.594666317089763</v>
+        <v>1.503934795302391</v>
       </c>
       <c r="G44">
-        <v>-2.926427401563424</v>
+        <v>-2.318886015832994</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.4759096929612</v>
       </c>
       <c r="E45">
-        <v>-16.3450263467789</v>
+        <v>-17.80698530999318</v>
       </c>
       <c r="F45">
-        <v>2.511941438596783</v>
+        <v>1.396706818885732</v>
       </c>
       <c r="G45">
-        <v>-2.25349280979577</v>
+        <v>-2.895811476416244</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.54214538471841</v>
       </c>
       <c r="E46">
-        <v>-15.04389160947304</v>
+        <v>-17.6052599068475</v>
       </c>
       <c r="F46">
-        <v>2.48744309179085</v>
+        <v>1.425083661478576</v>
       </c>
       <c r="G46">
-        <v>-2.864523510524593</v>
+        <v>-3.593846624462653</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.61087263934021</v>
       </c>
       <c r="E47">
-        <v>-14.77073858580437</v>
+        <v>-17.46139028762381</v>
       </c>
       <c r="F47">
-        <v>2.687693202562675</v>
+        <v>1.871568367982927</v>
       </c>
       <c r="G47">
-        <v>-3.562628180027326</v>
+        <v>-3.458435380269843</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.69165207147695</v>
       </c>
       <c r="E48">
-        <v>-14.3633298932303</v>
+        <v>-16.78177049397467</v>
       </c>
       <c r="F48">
-        <v>2.555673893745728</v>
+        <v>1.684627721724455</v>
       </c>
       <c r="G48">
-        <v>-4.061302275698823</v>
+        <v>-3.581581053239653</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.77789042004885</v>
       </c>
       <c r="E49">
-        <v>-13.29498136228872</v>
+        <v>-16.30591844524866</v>
       </c>
       <c r="F49">
-        <v>2.130483696980376</v>
+        <v>1.274751961161402</v>
       </c>
       <c r="G49">
-        <v>-3.321143746210728</v>
+        <v>-4.089971600068911</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.87926784106328</v>
       </c>
       <c r="E50">
-        <v>-12.81627184646388</v>
+        <v>-14.92168168142804</v>
       </c>
       <c r="F50">
-        <v>2.226826862640219</v>
+        <v>1.144846899741566</v>
       </c>
       <c r="G50">
-        <v>-3.631305447239506</v>
+        <v>-4.103419036049431</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.00164691529578</v>
       </c>
       <c r="E51">
-        <v>-11.43894553397896</v>
+        <v>-14.90840419563755</v>
       </c>
       <c r="F51">
-        <v>2.388946086086009</v>
+        <v>1.941020207198608</v>
       </c>
       <c r="G51">
-        <v>-3.879046812125326</v>
+        <v>-5.463699024317187</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.13475501203348</v>
       </c>
       <c r="E52">
-        <v>-12.03620144237659</v>
+        <v>-14.52479716244779</v>
       </c>
       <c r="F52">
-        <v>2.156659188350759</v>
+        <v>1.409302032031222</v>
       </c>
       <c r="G52">
-        <v>-3.926222086059941</v>
+        <v>-4.476994236882949</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.28530110788479</v>
       </c>
       <c r="E53">
-        <v>-12.12744566515714</v>
+        <v>-15.3214689522472</v>
       </c>
       <c r="F53">
-        <v>2.304765781856741</v>
+        <v>1.442901936733185</v>
       </c>
       <c r="G53">
-        <v>-3.827104352614161</v>
+        <v>-5.092312094085127</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-15.44845839553094</v>
       </c>
       <c r="E54">
-        <v>-11.37177920749719</v>
+        <v>-13.52346098987172</v>
       </c>
       <c r="F54">
-        <v>2.010204400114581</v>
+        <v>1.269066456924974</v>
       </c>
       <c r="G54">
-        <v>-4.378515438726248</v>
+        <v>-4.896413872344294</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-15.610051358659</v>
       </c>
       <c r="E55">
-        <v>-11.18269277530691</v>
+        <v>-12.90598544502984</v>
       </c>
       <c r="F55">
-        <v>2.017586053386444</v>
+        <v>1.320022194754239</v>
       </c>
       <c r="G55">
-        <v>-4.768143474879692</v>
+        <v>-5.271366260122148</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-15.7747445183515</v>
       </c>
       <c r="E56">
-        <v>-9.967458661452541</v>
+        <v>-14.29705114765403</v>
       </c>
       <c r="F56">
-        <v>2.225935236209827</v>
+        <v>1.314949584707086</v>
       </c>
       <c r="G56">
-        <v>-4.351706640949231</v>
+        <v>-5.9897380894163</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-15.9323531041131</v>
       </c>
       <c r="E57">
-        <v>-10.11995049518683</v>
+        <v>-13.11201742695681</v>
       </c>
       <c r="F57">
-        <v>2.405324772663484</v>
+        <v>0.8869150521176049</v>
       </c>
       <c r="G57">
-        <v>-4.507630025303365</v>
+        <v>-5.292828526853244</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.07153813272465</v>
       </c>
       <c r="E58">
-        <v>-9.199180403681227</v>
+        <v>-12.72693411124056</v>
       </c>
       <c r="F58">
-        <v>2.16219424052522</v>
+        <v>1.309799373070077</v>
       </c>
       <c r="G58">
-        <v>-4.590582364880882</v>
+        <v>-5.524242281139379</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.19631179995564</v>
       </c>
       <c r="E59">
-        <v>-9.484619177332705</v>
+        <v>-11.95724296957885</v>
       </c>
       <c r="F59">
-        <v>2.081754649668219</v>
+        <v>1.145767032878436</v>
       </c>
       <c r="G59">
-        <v>-5.174175264180225</v>
+        <v>-6.119402226552935</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.29475704463064</v>
       </c>
       <c r="E60">
-        <v>-9.21045177548632</v>
+        <v>-11.55617414061552</v>
       </c>
       <c r="F60">
-        <v>1.974312872952976</v>
+        <v>1.358848328977152</v>
       </c>
       <c r="G60">
-        <v>-5.667830572814188</v>
+        <v>-5.987841146822298</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.36237046979124</v>
       </c>
       <c r="E61">
-        <v>-10.11492388903832</v>
+        <v>-11.05230442320406</v>
       </c>
       <c r="F61">
-        <v>2.023886035518062</v>
+        <v>1.318156589185851</v>
       </c>
       <c r="G61">
-        <v>-5.247570058785867</v>
+        <v>-5.897330831778623</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.40219350142236</v>
       </c>
       <c r="E62">
-        <v>-8.752428328928517</v>
+        <v>-11.08276746785366</v>
       </c>
       <c r="F62">
-        <v>2.142923706946153</v>
+        <v>0.9051609279693827</v>
       </c>
       <c r="G62">
-        <v>-5.607505811997588</v>
+        <v>-6.049509989127841</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.40072555523289</v>
       </c>
       <c r="E63">
-        <v>-7.947560001175225</v>
+        <v>-11.42383401621536</v>
       </c>
       <c r="F63">
-        <v>1.944273139148921</v>
+        <v>1.035469834397656</v>
       </c>
       <c r="G63">
-        <v>-5.753954415018327</v>
+        <v>-6.411491659482832</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.35796303854385</v>
       </c>
       <c r="E64">
-        <v>-9.461410748043395</v>
+        <v>-10.78076353628212</v>
       </c>
       <c r="F64">
-        <v>1.593339745346694</v>
+        <v>0.9749326757799831</v>
       </c>
       <c r="G64">
-        <v>-5.036347321743748</v>
+        <v>-6.367348845262189</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.27415144777272</v>
       </c>
       <c r="E65">
-        <v>-8.305970604986303</v>
+        <v>-11.47952518956169</v>
       </c>
       <c r="F65">
-        <v>1.728857460530848</v>
+        <v>1.052588111637641</v>
       </c>
       <c r="G65">
-        <v>-5.861239264309488</v>
+        <v>-6.370351510066309</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-16.13766870378249</v>
       </c>
       <c r="E66">
-        <v>-8.308565420592698</v>
+        <v>-11.34878814496025</v>
       </c>
       <c r="F66">
-        <v>1.937808451602097</v>
+        <v>1.267599945247277</v>
       </c>
       <c r="G66">
-        <v>-6.35221965214772</v>
+        <v>-6.304690149840404</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.95784427324068</v>
       </c>
       <c r="E67">
-        <v>-7.941745440549377</v>
+        <v>-9.669788479506346</v>
       </c>
       <c r="F67">
-        <v>1.588048583883211</v>
+        <v>0.5309787313285045</v>
       </c>
       <c r="G67">
-        <v>-5.89212003309981</v>
+        <v>-6.824786785696525</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.73902581215641</v>
       </c>
       <c r="E68">
-        <v>-7.452022675937881</v>
+        <v>-9.136166687864494</v>
       </c>
       <c r="F68">
-        <v>1.74236488828363</v>
+        <v>0.720283850518728</v>
       </c>
       <c r="G68">
-        <v>-5.34653550713684</v>
+        <v>-6.600119923219425</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.47737190571961</v>
       </c>
       <c r="E69">
-        <v>-7.949914807659214</v>
+        <v>-9.895080061387947</v>
       </c>
       <c r="F69">
-        <v>1.587947226704623</v>
+        <v>0.8435151752109022</v>
       </c>
       <c r="G69">
-        <v>-6.173509782846783</v>
+        <v>-7.285085037476791</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.19021464811875</v>
       </c>
       <c r="E70">
-        <v>-8.00924687410771</v>
+        <v>-11.35376493789468</v>
       </c>
       <c r="F70">
-        <v>1.689617979064004</v>
+        <v>0.2318665706383292</v>
       </c>
       <c r="G70">
-        <v>-6.379068176471209</v>
+        <v>-6.375174974917027</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.88470300649231</v>
       </c>
       <c r="E71">
-        <v>-8.468058275142848</v>
+        <v>-10.66879701644247</v>
       </c>
       <c r="F71">
-        <v>1.349642246490703</v>
+        <v>0.5411849241005541</v>
       </c>
       <c r="G71">
-        <v>-5.337752629821154</v>
+        <v>-7.092384802726894</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.5636282498836</v>
       </c>
       <c r="E72">
-        <v>-9.139390961357956</v>
+        <v>-10.23875048230406</v>
       </c>
       <c r="F72">
-        <v>1.164457930092453</v>
+        <v>0.5005343606630543</v>
       </c>
       <c r="G72">
-        <v>-5.968186437955644</v>
+        <v>-7.355818153468859</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.24748705941844</v>
       </c>
       <c r="E73">
-        <v>-7.980726544807403</v>
+        <v>-10.61592708240292</v>
       </c>
       <c r="F73">
-        <v>1.313443480381503</v>
+        <v>0.5531228992911366</v>
       </c>
       <c r="G73">
-        <v>-6.250215122991696</v>
+        <v>-6.368408219834756</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.94031139516491</v>
       </c>
       <c r="E74">
-        <v>-8.333336173414654</v>
+        <v>-9.270549154042111</v>
       </c>
       <c r="F74">
-        <v>1.289353729701754</v>
+        <v>0.3169147457092584</v>
       </c>
       <c r="G74">
-        <v>-5.940536761611652</v>
+        <v>-8.001609582360029</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.64783729259381</v>
       </c>
       <c r="E75">
-        <v>-8.776533396071345</v>
+        <v>-11.71884145544504</v>
       </c>
       <c r="F75">
-        <v>1.13622995585566</v>
+        <v>0.5508138560664259</v>
       </c>
       <c r="G75">
-        <v>-5.481744808051754</v>
+        <v>-6.894573085664361</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.38448858746157</v>
       </c>
       <c r="E76">
-        <v>-9.837722409606794</v>
+        <v>-11.45699150289952</v>
       </c>
       <c r="F76">
-        <v>0.9446949787364977</v>
+        <v>0.3994076112856261</v>
       </c>
       <c r="G76">
-        <v>-4.810839580699673</v>
+        <v>-6.18297132199802</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.14737511735333</v>
       </c>
       <c r="E77">
-        <v>-8.971905350184267</v>
+        <v>-11.54243475047625</v>
       </c>
       <c r="F77">
-        <v>1.034845854266973</v>
+        <v>0.3465846841820588</v>
       </c>
       <c r="G77">
-        <v>-5.362177834809897</v>
+        <v>-6.457756533394146</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.94325676994614</v>
       </c>
       <c r="E78">
-        <v>-9.735143416385045</v>
+        <v>-11.65187438181962</v>
       </c>
       <c r="F78">
-        <v>0.7216410864882596</v>
+        <v>0.399908062354905</v>
       </c>
       <c r="G78">
-        <v>-4.310304958435105</v>
+        <v>-6.709602974748663</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.77942874095618</v>
       </c>
       <c r="E79">
-        <v>-8.87369633437992</v>
+        <v>-12.25223682338651</v>
       </c>
       <c r="F79">
-        <v>0.750372679206162</v>
+        <v>0.3188254868962361</v>
       </c>
       <c r="G79">
-        <v>-5.489527900614581</v>
+        <v>-5.417381181677244</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.64604324749659</v>
       </c>
       <c r="E80">
-        <v>-10.42506095992763</v>
+        <v>-12.67941230500407</v>
       </c>
       <c r="F80">
-        <v>1.12275261851527</v>
+        <v>0.2590429641472702</v>
       </c>
       <c r="G80">
-        <v>-4.614474572037802</v>
+        <v>-5.071257024455362</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.54974204267562</v>
       </c>
       <c r="E81">
-        <v>-11.91266467144734</v>
+        <v>-13.46959932002449</v>
       </c>
       <c r="F81">
-        <v>0.9520259534190669</v>
+        <v>0.2290626193150437</v>
       </c>
       <c r="G81">
-        <v>-5.089474956557972</v>
+        <v>-6.789092483692102</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.48987368282322</v>
       </c>
       <c r="E82">
-        <v>-11.59805346823845</v>
+        <v>-12.98574092925293</v>
       </c>
       <c r="F82">
-        <v>0.7672011382636216</v>
+        <v>0.1754224999591096</v>
       </c>
       <c r="G82">
-        <v>-3.958427073065971</v>
+        <v>-6.039899475427337</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.45607729826214</v>
       </c>
       <c r="E83">
-        <v>-13.40417192756167</v>
+        <v>-14.89199300583375</v>
       </c>
       <c r="F83">
-        <v>0.9406106011805794</v>
+        <v>0.4775880456542522</v>
       </c>
       <c r="G83">
-        <v>-4.61985089799358</v>
+        <v>-5.682737959377525</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.45737580691221</v>
       </c>
       <c r="E84">
-        <v>-13.78350860976219</v>
+        <v>-16.57481017487612</v>
       </c>
       <c r="F84">
-        <v>1.143826993132023</v>
+        <v>0.3178008291689468</v>
       </c>
       <c r="G84">
-        <v>-4.516714162263124</v>
+        <v>-5.296744902226202</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.49246066746824</v>
       </c>
       <c r="E85">
-        <v>-15.1823180029395</v>
+        <v>-15.6694414234706</v>
       </c>
       <c r="F85">
-        <v>0.9261181083483929</v>
+        <v>0.01770439525232593</v>
       </c>
       <c r="G85">
-        <v>-4.573678719357364</v>
+        <v>-6.101952341015436</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.55576339587277</v>
       </c>
       <c r="E86">
-        <v>-15.36582535515233</v>
+        <v>-16.30340514217441</v>
       </c>
       <c r="F86">
-        <v>1.292901230952338</v>
+        <v>0.4168069963256016</v>
       </c>
       <c r="G86">
-        <v>-3.968146834769271</v>
+        <v>-5.358188627435075</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.65600743804434</v>
       </c>
       <c r="E87">
-        <v>-17.57558028820123</v>
+        <v>-18.51284761051678</v>
       </c>
       <c r="F87">
-        <v>0.7334840393239158</v>
+        <v>0.1598451685748472</v>
       </c>
       <c r="G87">
-        <v>-3.926331334062737</v>
+        <v>-4.894175943559747</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.78438084245999</v>
       </c>
       <c r="E88">
-        <v>-18.1772242879123</v>
+        <v>-19.19063337219281</v>
       </c>
       <c r="F88">
-        <v>0.7972963017747174</v>
+        <v>-0.08458479426703482</v>
       </c>
       <c r="G88">
-        <v>-3.16346908326632</v>
+        <v>-4.515535608051144</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.93117504840043</v>
       </c>
       <c r="E89">
-        <v>-20.21519155948021</v>
+        <v>-22.28176520135459</v>
       </c>
       <c r="F89">
-        <v>1.111880477405778</v>
+        <v>0.2672156785238954</v>
       </c>
       <c r="G89">
-        <v>-3.634817936056673</v>
+        <v>-5.163412680632055</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.08928107409875</v>
       </c>
       <c r="E90">
-        <v>-21.96395689549628</v>
+        <v>-23.62208482424883</v>
       </c>
       <c r="F90">
-        <v>0.6184737320387876</v>
+        <v>-0.1894134562218027</v>
       </c>
       <c r="G90">
-        <v>-3.365826179354271</v>
+        <v>-3.921670085943443</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.23255338746704</v>
       </c>
       <c r="E91">
-        <v>-23.35642189658885</v>
+        <v>-25.85451835512814</v>
       </c>
       <c r="F91">
-        <v>0.6752685935782772</v>
+        <v>-0.009175053397470091</v>
       </c>
       <c r="G91">
-        <v>-2.955530407399158</v>
+        <v>-4.872763335011741</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.33975386058871</v>
       </c>
       <c r="E92">
-        <v>-24.87822464381449</v>
+        <v>-26.57129880648423</v>
       </c>
       <c r="F92">
-        <v>0.5033288097508473</v>
+        <v>0.09842351020340141</v>
       </c>
       <c r="G92">
-        <v>-3.500823605354672</v>
+        <v>-4.256581425423812</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.39000647478354</v>
       </c>
       <c r="E93">
-        <v>-26.56425250092829</v>
+        <v>-28.57460513799744</v>
       </c>
       <c r="F93">
-        <v>0.07339541376875409</v>
+        <v>0.0487972934901486</v>
       </c>
       <c r="G93">
-        <v>-3.073021668587892</v>
+        <v>-4.271409358894208</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.35287642035209</v>
       </c>
       <c r="E94">
-        <v>-29.85665915007199</v>
+        <v>-31.57796381970555</v>
       </c>
       <c r="F94">
-        <v>0.3544564944347506</v>
+        <v>-0.2425871741856399</v>
       </c>
       <c r="G94">
-        <v>-2.898291075025158</v>
+        <v>-4.246404808436093</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.22011249453656</v>
       </c>
       <c r="E95">
-        <v>-31.26619876241048</v>
+        <v>-34.11411304533129</v>
       </c>
       <c r="F95">
-        <v>0.2063443579580648</v>
+        <v>-0.128420982153441</v>
       </c>
       <c r="G95">
-        <v>-3.314115458030855</v>
+        <v>-4.3181443302721</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.98856013138876</v>
       </c>
       <c r="E96">
-        <v>-34.26656412279952</v>
+        <v>-35.53910381098395</v>
       </c>
       <c r="F96">
-        <v>0.1371894636015282</v>
+        <v>-0.1287020899534315</v>
       </c>
       <c r="G96">
-        <v>-3.09792028158875</v>
+        <v>-3.42742881074903</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.66122264258646</v>
       </c>
       <c r="E97">
-        <v>-36.75772069492206</v>
+        <v>-37.07095750626961</v>
       </c>
       <c r="F97">
-        <v>0.06145189560746751</v>
+        <v>-0.4997010377042765</v>
       </c>
       <c r="G97">
-        <v>-3.060064193347185</v>
+        <v>-4.664834590781196</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.26083687564074</v>
       </c>
       <c r="E98">
-        <v>-39.32464316566692</v>
+        <v>-40.65993844664965</v>
       </c>
       <c r="F98">
-        <v>-0.1437742191506687</v>
+        <v>-0.8003778998389059</v>
       </c>
       <c r="G98">
-        <v>-3.50982497867595</v>
+        <v>-5.130850154707783</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.81757501537523</v>
       </c>
       <c r="E99">
-        <v>-42.12205137798019</v>
+        <v>-44.10329498412803</v>
       </c>
       <c r="F99">
-        <v>-0.6363819848833202</v>
+        <v>-0.7442901629906602</v>
       </c>
       <c r="G99">
-        <v>-3.671300147899442</v>
+        <v>-4.793909450811841</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.34716546799102</v>
       </c>
       <c r="E100">
-        <v>-44.50386115247652</v>
+        <v>-45.75990587408801</v>
       </c>
       <c r="F100">
-        <v>-0.5835162977200361</v>
+        <v>-1.107462436107403</v>
       </c>
       <c r="G100">
-        <v>-3.925026979120264</v>
+        <v>-5.107484324291607</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.90274373041318</v>
       </c>
       <c r="E101">
-        <v>-47.26469514446683</v>
+        <v>-48.05872683391977</v>
       </c>
       <c r="F101">
-        <v>-0.7977085635184327</v>
+        <v>-0.8944452800982627</v>
       </c>
       <c r="G101">
-        <v>-4.086922587627242</v>
+        <v>-4.30115130001902</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.49645575906676</v>
       </c>
       <c r="E102">
-        <v>-48.69998026365743</v>
+        <v>-50.69645539213007</v>
       </c>
       <c r="F102">
-        <v>-1.019638816419667</v>
+        <v>-0.8344600429921205</v>
       </c>
       <c r="G102">
-        <v>-3.843365752303062</v>
+        <v>-4.191780807038119</v>
       </c>
     </row>
   </sheetData>
